--- a/examples/fyzioterapie/ladne-web.xlsx
+++ b/examples/fyzioterapie/ladne-web.xlsx
@@ -8122,26 +8122,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>show_folio</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>yes / no</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>Zobrazit malé číslo stránky (02 / 05) nahoře.</t>
-        </is>
-      </c>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="C20" s="15" t="n"/>

--- a/examples/fyzioterapie/ladne-web.xlsx
+++ b/examples/fyzioterapie/ladne-web.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1381,372 +1381,675 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Proměnné</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
+          <t>Barevné profily (styles › color_profile)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Do kteréhokoli textu můžete napsat proměnnou ve složených závorkách. Web ji při sestavení nahradí.</t>
+          <t>V listu styles vyberte v řádku color_profile jeden profil. Pozadí zůstává živé a jemně proměnlivé, profil mu dává základní tón. Kromě manual profily nepoužívají sloupec hue ani barvy textu z listu styles.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>proměnná</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>anglicky</t>
-        </is>
-      </c>
+          <t>profil</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr"/>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>co se dosadí</t>
+          <t>jak působí</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>příklad</t>
+          <t>barvy</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>{rok}</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>{year}</t>
-        </is>
-      </c>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr"/>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Aktuální rok. Mění se sám, i když web dlouho nepublikujete.</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>drobné: © {rok} {web}</t>
+          <t>Barvu každé stránky určuje sloupec hue v listu pages.</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>podle vás</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>{web}</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>{site}</t>
-        </is>
-      </c>
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>terakota</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr"/>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Název webu z listu site (site_name).</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>text: Vítejte na {web}.</t>
+          <t>Jedna barva v odstínech. Teplá cihlová.</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>#C8643B</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>(c)</t>
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>jantar</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr"/>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Napíše se jako ©.</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>drobné: (c) {rok} {web}</t>
+          <t>Jedna barva v odstínech. Medová, zlatavá.</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>#D9932E</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>koral</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr"/>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Jedna barva v odstínech. Svěží korálová.</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>#E8715A</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>Obrázky a média</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Obrázky nahrajte do složky media, která je ve složce klienta vedle této tabulky. Podsložky jsou v pořádku.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>V tabulce pak stačí název souboru: hero.jpg. Když je stejný název ve dvou podsložkách, napište cestu: galerie/hero.jpg.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Web obrázky sám zmenší a převede do rychlých formátů. Nahrávejte je v plné kvalitě, nic neupravujte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Používejte JPG, PNG nebo WebP. Fotky z iPhonu (HEIC) převeďte, nebo v iPhonu nastavte Fotoaparát → Formáty → Nejkompatibilnější.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Videa dávejte na YouTube nebo Vimeo a do stránky vložte odkaz.</t>
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>broskev</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr"/>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Jedna barva v odstínech. Jemná broskvová.</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>#E89B7A</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>karamel</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr"/>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Jedna barva v odstínech. Karamelově hnědá.</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>#B9773F</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>ruze</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr"/>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Jedna barva v odstínech. Prášková růže.</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>#C97B84</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>vinova</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr"/>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Jedna barva v odstínech. Hluboká vínová.</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>#9E3B5A</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>pisek</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr"/>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Jedna barva v odstínech. Světlý písek.</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>#C9A77A</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>tron</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr"/>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Neonově azurová s oranžovou, ubíhající mřížka v pozadí.</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>#00E5FF · #FF7A1A</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>matrix</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr"/>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Fosforově zelená, jemně padající znaky v pozadí.</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>#00FF41</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>Publikování</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="28" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Až budete s úpravami hotovi, klikněte v horním menu na Web → Publikovat. Za minutu až dvě je web online.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="28" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Výsledek se objeví v listu stav: kdy se publikovalo, jestli vše proběhlo a případná upozornění (třeba chybějící obrázek).</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="28" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Dokud nekliknete na Publikovat, návštěvníci vidí předchozí verzi. Upravovat tedy můžete v klidu.</t>
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>soumrak</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr"/>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Čtyři barvy se střídají po stránkách. Tlumená korálová, indigo, tyrkys, zlatá.</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>#D98B6A #7C78C8 #5BA8A0 #D9B86C</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>zeme</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr"/>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Čtyři barvy. Mech, okr, cihla, jezerní modrá.</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>#8FBF6F #E9A23B #C9583E #4F86C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>pastel</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr"/>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Čtyři barvy. Tlumená růžová, aqua, levandulová, světlá citronová.</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>#D9A3B8 #9CCBCF #A3B4D9 #DCD9A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>sever</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr"/>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Čtyři barvy. Severská modrá, šalvěj, pšeničná, tlumená červená.</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>#88C0D0 #A3BE8C #EBCB8B #BF616A</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
+          <t>Proměnné</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Do kteréhokoli textu můžete napsat proměnnou ve složených závorkách. Web ji při sestavení nahradí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>proměnná</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>anglicky</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>co se dosadí</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>příklad</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>{rok}</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>{year}</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Aktuální rok. Mění se sám, i když web dlouho nepublikujete.</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>drobné: © {rok} {web}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>{web}</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>{site}</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Název webu z listu site (site_name).</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>text: Vítejte na {web}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>(c)</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr"/>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Napíše se jako ©.</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>drobné: (c) {rok} {web}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Obrázky a média</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Obrázky nahrajte do složky media, která je ve složce klienta vedle této tabulky. Podsložky jsou v pořádku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>V tabulce pak stačí název souboru: hero.jpg. Když je stejný název ve dvou podsložkách, napište cestu: galerie/hero.jpg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Web obrázky sám zmenší a převede do rychlých formátů. Nahrávejte je v plné kvalitě, nic neupravujte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Používejte JPG, PNG nebo WebP. Fotky z iPhonu (HEIC) převeďte, nebo v iPhonu nastavte Fotoaparát → Formáty → Nejkompatibilnější.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Videa dávejte na YouTube nebo Vimeo a do stránky vložte odkaz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Publikování</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="28" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Až budete s úpravami hotovi, klikněte v horním menu na Web → Publikovat. Za minutu až dvě je web online.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="28" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Výsledek se objeví v listu stav: kdy se publikovalo, jestli vše proběhlo a případná upozornění (třeba chybějící obrázek).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="28" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Dokud nekliknete na Publikovat, návštěvníci vidí předchozí verzi. Upravovat tedy můžete v klidu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
           <t>Pravidla</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="28" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="95" ht="28" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>id: malá písmena, bez mezer a diakritiky, slova spojená pomlčkou (t-intro, img-hero).</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="28" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="96" ht="28" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>order: počítejte po desítkách (10, 20, 30). Když později něco vložíte mezi, dáte 15 a nic se nepřečísluje.</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="28" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="97" ht="28" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>visible: no skryje stránku nebo položku, aniž byste ji mazali.</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="28" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="98" ht="28" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Klíčové slovo s dvojtečkou vždy začíná nový kus. Nepište proto „poznámka:“ uprostřed běžné věty.</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="28" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="99" ht="28" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Názvy sloupců (tmavé záhlaví) neměňte, web je podle nich čte.</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="100" ht="28" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Pod patičkou každé stránky je drobný odkaz platform by filipmracek.com. Ten je součástí platformy, v tabulce se nenastavuje.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>Barvy v tabulce</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="8" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
         <is>
           <t>žluté buňky</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr"/>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Obsah stránky a texty. Tady skládáte.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>bílé buňky</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr"/>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Nastavení a údaje.</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="9" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
         <is>
           <t>šedé buňky</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr"/>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr"/>
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>Poznámky pro vás. Na webu se neobjeví.</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>roletky</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr"/>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr"/>
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Sloupce jako visible, kind a focus berou jen nabízené hodnoty.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="B78:D78"/>
+  <mergeCells count="22">
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="B87:D87"/>
     <mergeCell ref="A34:D34"/>
+    <mergeCell ref="B99:D99"/>
+    <mergeCell ref="B84:D84"/>
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="B92:D92"/>
     <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="B85:D85"/>
     <mergeCell ref="A54:D54"/>
+    <mergeCell ref="B97:D97"/>
     <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="B91:D91"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B96:D96"/>
     <mergeCell ref="A57:D57"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="B86:D86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7764,160 +8067,160 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>background</t>
+          <t>color_profile</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>drift</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>drift / still / solid</t>
+          <t>roletka (viz Návod)</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>drift: barvy se pomalu pohybují. still: stejné barvy bez pohybu. solid: jedna barva.</t>
+          <t>Barevný profil webu. manual = barvy podle sloupce hue v pages a nastavení níže. Ostatní profily nastaví barvy samy.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>background_speed</t>
+          <t>background</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>drift</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>slow / normal</t>
+          <t>drift / still / solid</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>Jak rychle se barvy pozadí mění.</t>
+          <t>drift: barvy se pomalu pohybují. still: stejné barvy bez pohybu. solid: jedna barva.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>background_follows_page</t>
+          <t>background_speed</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>yes / no</t>
+          <t>slow / normal</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Pozadí přebírá barvu stránky, která je vepředu.</t>
+          <t>Jak rychle se barvy pozadí mění.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>glass_opacity</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>0.62</v>
+          <t>background_follows_page</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>0.3 – 0.95</t>
+          <t>yes / no</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Jak plné jsou stránky. Méně = víc pozadí prosvítá.</t>
+          <t>Pozadí přebírá barvu stránky, která je vepředu.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>page_width</t>
+          <t>glass_opacity</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>860</v>
+        <v>0.62</v>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>640 – 1200 (px)</t>
+          <t>0.3 – 0.95</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Největší šířka stránky na počítači.</t>
+          <t>Jak plné jsou stránky. Méně = víc pozadí prosvítá.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>page_radius</t>
+          <t>page_width</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>22</v>
+        <v>860</v>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>0 – 40 (px)</t>
+          <t>640 – 1200 (px)</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Zaoblení rohů stránky.</t>
+          <t>Největší šířka stránky na počítači.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>font_display</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Fraunces</t>
-        </is>
+          <t>page_radius</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>22</v>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>libovolný Google Font</t>
+          <t>0 – 40 (px)</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Písmo nadpisů.</t>
+          <t>Zaoblení rohů stránky.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>font_body</t>
+          <t>font_display</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Figtree</t>
+          <t>Fraunces</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -7927,19 +8230,19 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Písmo textu.</t>
+          <t>Písmo nadpisů.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>font_utility</t>
+          <t>font_body</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>JetBrains Mono</t>
+          <t>Figtree</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
@@ -7949,61 +8252,61 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Písmo malých popisků a čísel.</t>
+          <t>Písmo textu.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>text_size</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>17</v>
+          <t>font_utility</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>JetBrains Mono</t>
+        </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>14 – 20 (px)</t>
+          <t>libovolný Google Font</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Základní velikost textu. Nadpisy se odvodí.</t>
+          <t>Písmo malých popisků a čísel.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>text_color</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>#ECE9F4</t>
-        </is>
+          <t>text_size</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>17</v>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>hex barva</t>
+          <t>14 – 20 (px)</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Hlavní barva textu.</t>
+          <t>Základní velikost textu. Nadpisy se odvodí.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>muted_color</t>
+          <t>text_color</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>#A29FB7</t>
+          <t>#ECE9F4</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -8013,117 +8316,135 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Barva popisků a vedlejšího textu.</t>
+          <t>Hlavní barva textu.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>hue_saturation</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>70</v>
+          <t>muted_color</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>#A29FB7</t>
+        </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>0 – 100</t>
+          <t>hex barva</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Jak syté jsou barvy stránek. 0 = jen šedé.</t>
+          <t>Barva popisků a vedlejšího textu.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>turn_speed</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
+          <t>hue_saturation</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>70</v>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>slow / normal / quick</t>
+          <t>0 – 100</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Rychlost otočení.</t>
+          <t>Jak syté jsou barvy stránek. 0 = jen šedé.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>turn_angle</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>30</v>
+          <t>turn_speed</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>0 – 45 (stupňů)</t>
+          <t>slow / normal / quick</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Jak moc se stoh natočí bokem. 0 natočení vypne.</t>
+          <t>Rychlost otočení.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>stack_depth</t>
+          <t>turn_angle</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>1 – 8</t>
+          <t>0 – 45 (stupňů)</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>Kolik stránek je při otáčení vidět za tou přední.</t>
+          <t>Jak moc se stoh natočí bokem. 0 natočení vypne.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
+          <t>stack_depth</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>1 – 8</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Kolik stránek je při otáčení vidět za tou přední.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
           <t>tabs_desktop</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>right / left</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Na které straně jsou záložky na počítači.</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="C20" s="15" t="n"/>
@@ -8846,6 +9167,11 @@
       <c r="D199" s="15" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Neznámý profil" error="Vyberte jeden z nabízených profilů." type="list">
+      <formula1>"manual,terakota,jantar,koral,broskev,karamel,ruze,vinova,pisek,tron,matrix,soumrak,zeme,pastel,sever"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/examples/fyzioterapie/ladne-web.xlsx
+++ b/examples/fyzioterapie/ladne-web.xlsx
@@ -1437,7 +1437,7 @@
       <c r="B60" s="5" t="inlineStr"/>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech. Teplá cihlová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Teplá cihlová.</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -1455,7 +1455,7 @@
       <c r="B61" s="5" t="inlineStr"/>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech. Medová, zlatavá.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Medová, zlatavá.</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -1473,7 +1473,7 @@
       <c r="B62" s="5" t="inlineStr"/>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech. Svěží korálová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Svěží korálová.</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -1491,7 +1491,7 @@
       <c r="B63" s="5" t="inlineStr"/>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech. Jemná broskvová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Jemná broskvová.</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -1509,7 +1509,7 @@
       <c r="B64" s="5" t="inlineStr"/>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech. Karamelově hnědá.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Karamelově hnědá.</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -1527,7 +1527,7 @@
       <c r="B65" s="5" t="inlineStr"/>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech. Prášková růže.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Prášková růže.</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -1545,7 +1545,7 @@
       <c r="B66" s="5" t="inlineStr"/>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech. Hluboká vínová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Hluboká vínová.</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -1563,7 +1563,7 @@
       <c r="B67" s="5" t="inlineStr"/>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech. Světlý písek.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Světlý písek.</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -1575,36 +1575,36 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>tron</t>
+          <t>seda</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr"/>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Neonově azurová s oranžovou, ubíhající mřížka v pozadí.</t>
+          <t>Stupně šedi, bez barvy. Pozadí v tmavě šedých tónech.</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>#00E5FF · #FF7A1A</t>
+          <t>#9C9C9E</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>matrix</t>
+          <t>tron</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr"/>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Fosforově zelená, jemně padající znaky v pozadí.</t>
+          <t>Neonově azurová s oranžovou, záře na hranách, pozadí v modrých a oranžových tónech.</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>#00FF41</t>
+          <t>#00E5FF · #FF7A1A</t>
         </is>
       </c>
     </row>
@@ -9169,7 +9169,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Neznámý profil" error="Vyberte jeden z nabízených profilů." type="list">
-      <formula1>"manual,terakota,jantar,koral,broskev,karamel,ruze,vinova,pisek,tron,matrix,soumrak,zeme,pastel,sever"</formula1>
+      <formula1>"manual,terakota,jantar,koral,broskev,karamel,ruze,vinova,pisek,seda,tron,soumrak,zeme,pastel,sever"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
